--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_188_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_188_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2984</v>
+        <v>9.859500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9761</v>
+        <v>10.2684</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6777</v>
+        <v>-0.4089</v>
       </c>
       <c r="G2" t="n">
         <v>7.6906</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0211</v>
+        <v>-0.4599</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1053</v>
+        <v>0.3976</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1264</v>
+        <v>-0.8575</v>
       </c>
       <c r="V2" t="n">
         <v>2.3969</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3934</v>
+        <v>2.5614</v>
       </c>
       <c r="E3" t="n">
         <v>2.5527</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1593</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.0466</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3465</v>
+        <v>-1.1784</v>
       </c>
       <c r="T3" t="n">
         <v>-0.2513</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0952</v>
+        <v>-0.9271</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9443</v>
+        <v>1.1123</v>
       </c>
       <c r="E4" t="n">
         <v>0.8982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0461</v>
+        <v>0.2141</v>
       </c>
       <c r="G4" t="n">
         <v>1.2625</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0294</v>
+        <v>0.1386</v>
       </c>
       <c r="T4" t="n">
         <v>0.3541</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3835</v>
+        <v>-0.2155</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1444</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6018</v>
+        <v>0.5682</v>
       </c>
       <c r="E5" t="n">
         <v>-0.5663</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1681</v>
+        <v>1.1344</v>
       </c>
       <c r="G5" t="n">
         <v>2.0084</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2623</v>
+        <v>-0.2959</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2271</v>
+        <v>-0.2607</v>
       </c>
       <c r="V5" t="n">
         <v>-1.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0196</v>
+        <v>-0.0868</v>
       </c>
       <c r="E6" t="n">
         <v>-2.3295</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3099</v>
+        <v>2.2427</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4486</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.246</v>
+        <v>0.1788</v>
       </c>
       <c r="T6" t="n">
         <v>0.586</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.34</v>
+        <v>-0.4072</v>
       </c>
       <c r="V6" t="n">
         <v>1.1829</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5144</v>
+        <v>-2.2065</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3396</v>
+        <v>-1.706</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.854</v>
+        <v>-0.5004</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7364</v>
+        <v>-4.0053</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1405</v>
+        <v>0.1103</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5959</v>
+        <v>-4.1156</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4519</v>
+        <v>-2.7042</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4151</v>
+        <v>1.3514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0368</v>
+        <v>-4.0556</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1883</v>
+        <v>-1.3011</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5556</v>
+        <v>-1.241</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6327</v>
+        <v>-0.06</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0622</v>
+        <v>-1.1136</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5113</v>
+        <v>-0.5226</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.5911</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6083</v>
+        <v>2.6805</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5811</v>
+        <v>-2.396</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0707</v>
+        <v>-1.9528</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5104</v>
+        <v>-0.4432</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0206</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.0885</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7626</v>
+        <v>-3.2208</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2958</v>
+        <v>1.1037</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4668</v>
+        <v>-4.3245</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0053</v>
+        <v>-1.7364</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1103</v>
+        <v>-0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.1156</v>
+        <v>-1.5959</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7042</v>
+        <v>1.4519</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3514</v>
+        <v>1.4151</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.0556</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3011</v>
+        <v>-3.1883</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.241</v>
+        <v>-1.5556</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06</v>
+        <v>-1.6327</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6698</v>
+        <v>0.3558</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1123</v>
+        <v>0.2754</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5575</v>
+        <v>0.0804</v>
       </c>
       <c r="V9" t="n">
-        <v>2.6805</v>
+        <v>-1.6083</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6805</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5516</v>
+        <v>-3.315</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7827</v>
+        <v>-2.3109</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7689</v>
+        <v>-1.0042</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1416</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5698</v>
+        <v>-0.3332</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1691</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5886</v>
+        <v>-3.437</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9197</v>
+        <v>-1.8018</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6689</v>
+        <v>-1.6353</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2272</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4336</v>
+        <v>-0.282</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.677</v>
+        <v>-4.8964</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3067</v>
+        <v>-4.6605</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3703</v>
+        <v>-0.2359</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9474</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3585</v>
+        <v>-0.5779</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3383</v>
+        <v>-0.0156</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6967</v>
+        <v>-0.5623</v>
       </c>
       <c r="V12" t="n">
         <v>0.2525</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.457000000000001</v>
+        <v>-5.4571</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5048000000000012</v>
+        <v>-0.5048000000000004</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.9522</v>
+        <v>-4.9525</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.519000000000002</v>
+        <v>-4.519</v>
       </c>
       <c r="H13" t="n">
         <v>1.002</v>
@@ -1447,7 +1447,7 @@
         <v>6.690100000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.6314</v>
+        <v>-3.631400000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-7.577599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.4794</v>
+        <v>-3.4792</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4743999999999997</v>
+        <v>0.4743999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.9537</v>
+        <v>-3.9536</v>
       </c>
       <c r="V13" t="n">
         <v>0.2213999999999997</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.385300000000001</v>
+        <v>8.163600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6143</v>
+        <v>4.569</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7709</v>
+        <v>3.5947</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7837</v>
+        <v>5.7956</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9868</v>
+        <v>1.6434</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7969</v>
+        <v>4.1522</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6873</v>
+        <v>4.6062</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2519</v>
+        <v>2.7595</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4354</v>
+        <v>1.8467</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0964</v>
+        <v>1.1894</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2651</v>
+        <v>-1.1161</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3615</v>
+        <v>2.3055</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0681</v>
+        <v>1.2237</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4812</v>
+        <v>0.6018</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5869</v>
+        <v>0.6218</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.6083</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3894</v>
+        <v>7.9762</v>
       </c>
       <c r="E15" t="n">
-        <v>4.569</v>
+        <v>5.3169</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8204</v>
+        <v>2.6593</v>
       </c>
       <c r="G15" t="n">
-        <v>5.7956</v>
+        <v>3.7837</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6434</v>
+        <v>1.9868</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1522</v>
+        <v>1.7969</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6062</v>
+        <v>3.6873</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7595</v>
+        <v>2.2519</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8467</v>
+        <v>1.4354</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1894</v>
+        <v>0.0964</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1161</v>
+        <v>-0.2651</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3055</v>
+        <v>0.3615</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4494</v>
+        <v>1.659</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6018</v>
+        <v>1.1837</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1524</v>
+        <v>0.4753</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6083</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1444</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3243</v>
+        <v>4.3764</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4667</v>
+        <v>2.5847</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8576</v>
+        <v>1.7917</v>
       </c>
       <c r="G16" t="n">
         <v>2.1917</v>
@@ -1702,13 +1702,13 @@
         <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0605</v>
+        <v>1.1125</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5351</v>
+        <v>0.653</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5254</v>
+        <v>0.4595</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2224</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1228</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9005</v>
+        <v>1.6855</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1219</v>
+        <v>2.3414</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2797</v>
+        <v>-0.0143</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4016</v>
+        <v>2.3556</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8300999999999999</v>
+        <v>1.0159</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7933</v>
+        <v>0.4404</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>0.5754</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7082000000000001</v>
+        <v>1.3255</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.073</v>
+        <v>-0.4547</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3648</v>
+        <v>1.7802</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-2.7834</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0282</v>
+        <v>1.1745</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6122</v>
+        <v>0.8298</v>
       </c>
       <c r="U17" t="n">
-        <v>0.416</v>
+        <v>0.3446</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. LARENTZAKIS</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.168</v>
+        <v>-0.0795</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.168</v>
+        <v>-1.0228</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.168</v>
+        <v>0.1219</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.168</v>
+        <v>-0.2797</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.4016</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.7933</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.168</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.168</v>
+        <v>-1.073</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.3648</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.7264</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.4327</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.2937</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>G. LARENTZAKIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2335</v>
+        <v>-0.168</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5036</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2702</v>
+        <v>-0.168</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3414</v>
+        <v>-0.168</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0143</v>
+        <v>-0.168</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3556</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0159</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4404</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5754</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3255</v>
+        <v>-0.168</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4547</v>
+        <v>-0.168</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7802</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7834</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0514</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1221</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0707</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6234</v>
+        <v>-1.1946</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3749</v>
+        <v>-1.8274</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2485</v>
+        <v>0.6328</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2342</v>
+        <v>0.2579</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9699</v>
+        <v>0.3986</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2643</v>
+        <v>-0.1407</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7695</v>
+        <v>-0.8605</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7695</v>
+        <v>0.6421</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.5026</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4647</v>
+        <v>1.1184</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2004</v>
+        <v>-0.2435</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2643</v>
+        <v>1.3619</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1573</v>
+        <v>1.1558</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>0.6567</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2161</v>
+        <v>0.4991</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MORRIS</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0024</v>
+        <v>-1.2696</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0722</v>
+        <v>-1.021</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0745</v>
+        <v>-0.2485</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7864</v>
+        <v>-1.2342</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2004</v>
+        <v>-0.9699</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.586</v>
+        <v>-0.2643</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7849</v>
+        <v>-0.7695</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4636</v>
+        <v>-0.7695</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3213</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0016</v>
+        <v>-0.4647</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7369</v>
+        <v>-0.2004</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2647</v>
+        <v>-0.2643</v>
       </c>
       <c r="P21" t="n">
         <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1964</v>
+        <v>0.1966</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9831</v>
+        <v>-0.0196</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.2161</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.0336</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>M. MORRIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6658</v>
+        <v>-2.3176</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0069</v>
+        <v>0.3644</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3411</v>
+        <v>-2.682</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2579</v>
+        <v>-2.7864</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3986</v>
+        <v>-1.2004</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1407</v>
+        <v>-1.586</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8605</v>
+        <v>-0.7849</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6421</v>
+        <v>-0.4636</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5026</v>
+        <v>-0.3213</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1184</v>
+        <v>-2.0016</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2435</v>
+        <v>-0.7369</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3619</v>
+        <v>-1.2647</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3154</v>
+        <v>-0.1188</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5228</v>
+        <v>0.2754</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2074</v>
+        <v>-0.3943</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1444</v>
+        <v>0.8197</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.0336</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1486</v>
+        <v>-2.6603</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1892</v>
+        <v>0.1646</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9593</v>
+        <v>-2.8249</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3287</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9796</v>
+        <v>-0.4914</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0226</v>
+        <v>-5.9001</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.818</v>
+        <v>-5.3462</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2045</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4559</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9224</v>
+        <v>-0.8</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8883</v>
+        <v>-0.4165</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0341</v>
+        <v>-0.3835</v>
       </c>
       <c r="V24" t="n">
         <v>0.2836</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.457100000000003</v>
+        <v>7.8161</v>
       </c>
       <c r="E25" t="n">
-        <v>4.952399999999999</v>
+        <v>4.952400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5049000000000006</v>
+        <v>2.863899999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>4.519</v>
+        <v>4.519000000000002</v>
       </c>
       <c r="H25" t="n">
         <v>-1.0019</v>
       </c>
       <c r="I25" t="n">
-        <v>5.520699999999999</v>
+        <v>5.520700000000001</v>
       </c>
       <c r="J25" t="n">
         <v>7.5777</v>
@@ -2383,7 +2383,7 @@
         <v>5.688400000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.889299999999999</v>
+        <v>1.889300000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-3.0589</v>
@@ -2392,7 +2392,7 @@
         <v>-6.690300000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>3.631499999999999</v>
+        <v>3.6315</v>
       </c>
       <c r="P25" t="n">
         <v>-2.3196</v>
@@ -2404,22 +2404,22 @@
         <v>12.7575</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4793</v>
+        <v>5.8383</v>
       </c>
       <c r="T25" t="n">
-        <v>3.953499999999999</v>
+        <v>3.9534</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4743999999999999</v>
+        <v>1.8845</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2213999999999999</v>
+        <v>-0.2214</v>
       </c>
       <c r="W25" t="n">
         <v>8.4979</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.7194</v>
+        <v>-8.719400000000002</v>
       </c>
     </row>
   </sheetData>
